--- a/03_Group_comparisons/Proteome_clusters/c_data/05_module_classification_all_inputs.xlsx
+++ b/03_Group_comparisons/Proteome_clusters/c_data/05_module_classification_all_inputs.xlsx
@@ -315,31 +315,31 @@
     <t>03_Group_comparisons/Proteome_T1/c_data/05_module_classification.xlsx</t>
   </si>
   <si>
-    <t>315de5056acfbaf31560a0b85c700f5c</t>
+    <t>be6854191a84d1f2dbcba8dd44ff18ce</t>
   </si>
   <si>
     <t>03_Group_comparisons/Proteome_T2/c_data/05_module_classification.xlsx</t>
   </si>
   <si>
-    <t>bce496d8036312fb9d50e648e01f1fed</t>
+    <t>d3456e0b0e3796da2eaeb960f27f7cda</t>
   </si>
   <si>
     <t>03_Group_comparisons/Proteome_T3/c_data/05_module_classification.xlsx</t>
   </si>
   <si>
-    <t>599e140ce6883276d01e4335d98f86d4</t>
+    <t>e9dfc66122055eca440be3f3cc1b9b50</t>
   </si>
   <si>
     <t>03_Group_comparisons/Proteome_training/c_data/05_module_classification.xlsx</t>
   </si>
   <si>
-    <t>67b54697b2ccc74b6f199c5ae1d52020</t>
+    <t>a3da2be49521b5830e42a00c36d86af1</t>
   </si>
   <si>
     <t>03_Group_comparisons/Proteome_acute/c_data/05_module_classification.xlsx</t>
   </si>
   <si>
-    <t>60e75e8932ef13b16dd2f4b92e3d64bc</t>
+    <t>697f30eff2d899002aa5c8759a5d2fb4</t>
   </si>
   <si>
     <t>BiocGenerics</t>
